--- a/doctool/test/auto/scenario29/レビュー記録サマリ_S29_expected.xlsx
+++ b/doctool/test/auto/scenario29/レビュー記録サマリ_S29_expected.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99076773-E0D6-4AA2-AB31-620048FB4BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84857BF1-B37A-4C8C-BF71-1BE0EFABC6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9300" yWindow="4320" windowWidth="38700" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3630" yWindow="3630" windowWidth="38700" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="品質指標" sheetId="4" r:id="rId1"/>
@@ -720,9 +720,6 @@
     <t>D00001</t>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S28</t>
-  </si>
-  <si>
     <t>鈴木　花子</t>
   </si>
   <si>
@@ -730,6 +727,10 @@
   </si>
   <si>
     <t>回覧</t>
+  </si>
+  <si>
+    <t>システム機能設計書_サンプル_S29</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -1158,13 +1159,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1840,40 +1841,40 @@
       <c r="AB4" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="AC4" s="64" t="s">
+      <c r="AC4" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="AD4" s="66" t="s">
+      <c r="AD4" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="AE4" s="66" t="s">
+      <c r="AE4" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="AF4" s="66" t="s">
+      <c r="AF4" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="AG4" s="66" t="s">
+      <c r="AG4" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="AH4" s="66" t="s">
+      <c r="AH4" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="AI4" s="66" t="s">
+      <c r="AI4" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="AJ4" s="66" t="s">
+      <c r="AJ4" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="AK4" s="66" t="s">
+      <c r="AK4" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="AL4" s="66" t="s">
+      <c r="AL4" s="64" t="s">
         <v>97</v>
       </c>
-      <c r="AM4" s="66" t="s">
+      <c r="AM4" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="AN4" s="66" t="s">
+      <c r="AN4" s="64" t="s">
         <v>99</v>
       </c>
       <c r="AO4" s="7" t="s">
@@ -1957,18 +1958,18 @@
       <c r="AB5" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="AC5" s="65"/>
-      <c r="AD5" s="66"/>
-      <c r="AE5" s="66"/>
-      <c r="AF5" s="66"/>
-      <c r="AG5" s="66"/>
-      <c r="AH5" s="66"/>
-      <c r="AI5" s="66"/>
-      <c r="AJ5" s="66"/>
-      <c r="AK5" s="66"/>
-      <c r="AL5" s="66"/>
-      <c r="AM5" s="66"/>
-      <c r="AN5" s="66"/>
+      <c r="AC5" s="66"/>
+      <c r="AD5" s="64"/>
+      <c r="AE5" s="64"/>
+      <c r="AF5" s="64"/>
+      <c r="AG5" s="64"/>
+      <c r="AH5" s="64"/>
+      <c r="AI5" s="64"/>
+      <c r="AJ5" s="64"/>
+      <c r="AK5" s="64"/>
+      <c r="AL5" s="64"/>
+      <c r="AM5" s="64"/>
+      <c r="AN5" s="64"/>
       <c r="AO5" s="18" t="s">
         <v>14</v>
       </c>
@@ -2008,10 +2009,10 @@
       </c>
       <c r="E6" s="43"/>
       <c r="F6" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" s="44" t="s">
         <v>102</v>
-      </c>
-      <c r="G6" s="44" t="s">
-        <v>103</v>
       </c>
       <c r="H6" s="45">
         <v>1</v>
@@ -2039,7 +2040,7 @@
         <v>200</v>
       </c>
       <c r="Q6" s="52" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R6" s="53"/>
       <c r="S6" s="53"/>
@@ -2047,11 +2048,11 @@
       <c r="U6" s="53"/>
       <c r="V6" s="53"/>
       <c r="W6" s="54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="X6" s="53"/>
       <c r="Y6" s="55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Z6" s="56">
         <f t="shared" ref="Z6" si="1">IF(Y6="回覧",COUNTA(Q6:V6),COUNTA(Q6:X6))</f>
